--- a/OpticaII/P2_Espectros/p2optica.xlsx
+++ b/OpticaII/P2_Espectros/p2optica.xlsx
@@ -6,6 +6,7 @@
     <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="h1input" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Hoja 2" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="h2input" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="48">
   <si>
     <t>ang referencia</t>
   </si>
@@ -70,6 +71,9 @@
   </si>
   <si>
     <t>media -&gt;</t>
+  </si>
+  <si>
+    <t>errortheta es 0.1 grados</t>
   </si>
   <si>
     <t xml:space="preserve">cte </t>
@@ -406,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="107">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -684,6 +688,27 @@
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,6 +727,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1729,6 +1758,9 @@
       </c>
     </row>
     <row r="16">
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G16" s="25">
         <f t="shared" ref="G16:G25" si="11">(SIN((D3-$B$1)*PI()/180))/(B3*D3/10^6)</f>
         <v>1014.636501</v>
@@ -1752,7 +1784,7 @@
         <v>1961.628547</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -2213,7 +2245,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1">
         <v>54.7</v>
@@ -2224,16 +2256,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2244,7 +2276,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="34" t="s">
         <v>6</v>
@@ -2253,19 +2285,19 @@
         <v>7</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="23" t="s">
         <v>2</v>
@@ -2274,7 +2306,7 @@
         <v>3</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3" s="34" t="s">
         <v>6</v>
@@ -2283,19 +2315,19 @@
         <v>7</v>
       </c>
       <c r="R3" s="34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S3" s="34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T3" s="34" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V3" s="34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2303,7 +2335,7 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="38">
         <v>70.2</v>
@@ -2337,7 +2369,7 @@
         <v>-1.0</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" s="38">
         <v>39.3</v>
@@ -2380,7 +2412,7 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="45">
         <v>70.5</v>
@@ -2414,7 +2446,7 @@
         <v>-1.0</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" s="45">
         <v>39.1</v>
@@ -2453,7 +2485,7 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="52">
         <v>71.4</v>
@@ -2487,7 +2519,7 @@
         <v>-1.0</v>
       </c>
       <c r="N6" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6" s="52">
         <v>38.2</v>
@@ -2523,7 +2555,7 @@
         <v>1.0</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="58">
         <v>72.0</v>
@@ -2557,7 +2589,7 @@
         <v>-1.0</v>
       </c>
       <c r="N7" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O7" s="58">
         <v>37.4</v>
@@ -2593,7 +2625,7 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="64">
         <v>72.5</v>
@@ -2627,7 +2659,7 @@
         <v>-1.0</v>
       </c>
       <c r="N8" s="63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O8" s="64">
         <v>37.1</v>
@@ -2663,10 +2695,10 @@
         <v>1.0</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="70"/>
       <c r="F9" s="71">
@@ -2695,13 +2727,13 @@
         <v>-1.0</v>
       </c>
       <c r="N9" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O9" s="70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P9" s="70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q9" s="70">
         <v>54.7</v>
@@ -2738,7 +2770,7 @@
         <v>1.0</v>
       </c>
       <c r="C10" s="77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="78">
         <v>75.7</v>
@@ -2772,7 +2804,7 @@
         <v>-1.0</v>
       </c>
       <c r="N10" s="77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" s="78">
         <v>33.9</v>
@@ -2894,7 +2926,7 @@
         <v>1.0</v>
       </c>
       <c r="C12" s="90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="91">
         <v>80.1</v>
@@ -2928,7 +2960,7 @@
         <v>-1.0</v>
       </c>
       <c r="N12" s="90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O12" s="91">
         <v>29.5</v>
@@ -2972,7 +3004,7 @@
         <v>2.0</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="38">
         <v>87.0</v>
@@ -3006,7 +3038,7 @@
         <v>-2.0</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O13" s="38">
         <v>22.8</v>
@@ -3050,7 +3082,7 @@
         <v>2.0</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="45">
         <v>87.7</v>
@@ -3084,7 +3116,7 @@
         <v>-2.0</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O14" s="45">
         <v>22.1</v>
@@ -3128,7 +3160,7 @@
         <v>2.0</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="52">
         <v>89.8</v>
@@ -3162,7 +3194,7 @@
         <v>-2.0</v>
       </c>
       <c r="N15" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O15" s="52">
         <v>20.2</v>
@@ -3206,7 +3238,7 @@
         <v>2.0</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="58">
         <v>91.6</v>
@@ -3240,7 +3272,7 @@
         <v>-2.0</v>
       </c>
       <c r="N16" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O16" s="58">
         <v>18.4</v>
@@ -3284,7 +3316,7 @@
         <v>2.0</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="64">
         <v>92.5</v>
@@ -3318,7 +3350,7 @@
         <v>-2.0</v>
       </c>
       <c r="N17" s="63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O17" s="64">
         <v>17.6</v>
@@ -3354,7 +3386,7 @@
         <v>2.0</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="70">
         <v>92.7</v>
@@ -3388,7 +3420,7 @@
         <v>-2.0</v>
       </c>
       <c r="N18" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O18" s="70">
         <v>17.3</v>
@@ -3424,7 +3456,7 @@
         <v>2.0</v>
       </c>
       <c r="C19" s="77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="78">
         <v>100.6</v>
@@ -3458,7 +3490,7 @@
         <v>-2.0</v>
       </c>
       <c r="N19" s="77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O19" s="78">
         <v>9.8</v>
@@ -3489,7 +3521,7 @@
         <v>588.7412041</v>
       </c>
       <c r="Y19" s="75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z19" s="82">
         <v>707.0</v>
@@ -3565,7 +3597,7 @@
         <v>668.1463702</v>
       </c>
       <c r="Y20" s="75" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z20" s="82">
         <v>668.0</v>
@@ -3576,7 +3608,7 @@
         <v>2.0</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="91"/>
       <c r="E21" s="91"/>
@@ -3613,7 +3645,7 @@
       <c r="U21" s="91"/>
       <c r="V21" s="94"/>
       <c r="Y21" s="75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z21" s="82">
         <v>588.0</v>
@@ -3624,7 +3656,7 @@
         <v>3.0</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" s="38">
         <v>109.8</v>
@@ -3658,7 +3690,7 @@
         <v>-3.0</v>
       </c>
       <c r="N22" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O22" s="37"/>
       <c r="P22" s="38">
@@ -3684,7 +3716,7 @@
         <v>438.9750069</v>
       </c>
       <c r="Y22" s="75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z22" s="82">
         <v>502.0</v>
@@ -3695,7 +3727,7 @@
         <v>3.0</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" s="45"/>
       <c r="E23" s="45"/>
@@ -3719,7 +3751,7 @@
         <v>-3.0</v>
       </c>
       <c r="N23" s="97" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O23" s="44">
         <v>1.0</v>
@@ -3750,7 +3782,7 @@
         <v>447.450748</v>
       </c>
       <c r="Y23" s="75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z23" s="82">
         <v>492.0</v>
@@ -3761,7 +3793,7 @@
         <v>3.0</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="52"/>
       <c r="E24" s="52">
@@ -3790,7 +3822,7 @@
         <v>-3.0</v>
       </c>
       <c r="N24" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O24" s="52"/>
       <c r="P24" s="52">
@@ -3816,7 +3848,7 @@
         <v>471.1378312</v>
       </c>
       <c r="Y24" s="75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z24" s="82">
         <v>470.0</v>
@@ -3827,7 +3859,7 @@
         <v>3.0</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" s="58"/>
       <c r="E25" s="58"/>
@@ -3851,7 +3883,7 @@
         <v>-3.0</v>
       </c>
       <c r="N25" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O25" s="58">
         <v>352.4</v>
@@ -3882,7 +3914,7 @@
         <v>491.6597986</v>
       </c>
       <c r="Y25" s="75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Z25" s="82">
         <v>447.0</v>
@@ -3893,7 +3925,7 @@
         <v>3.0</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" s="64">
         <v>122.2</v>
@@ -3927,7 +3959,7 @@
         <v>-3.0</v>
       </c>
       <c r="N26" s="63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O26" s="64">
         <v>350.3</v>
@@ -3958,7 +3990,7 @@
         <v>500.8083984</v>
       </c>
       <c r="Y26" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z26" s="82">
         <v>403.0</v>
@@ -3969,7 +4001,7 @@
         <v>3.0</v>
       </c>
       <c r="C27" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
@@ -3993,7 +4025,7 @@
         <v>-3.0</v>
       </c>
       <c r="N27" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O27" s="70">
         <v>349.6</v>
@@ -4029,7 +4061,7 @@
         <v>3.0</v>
       </c>
       <c r="C28" s="77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" s="78"/>
       <c r="E28" s="78"/>
@@ -4101,7 +4133,7 @@
         <v>3.0</v>
       </c>
       <c r="C30" s="90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" s="91"/>
       <c r="E30" s="91"/>
@@ -4141,4 +4173,724 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="38">
+        <v>70.2</v>
+      </c>
+      <c r="D2" s="38">
+        <v>70.1</v>
+      </c>
+      <c r="E2" s="39">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43">
+        <v>1.0</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="45">
+        <v>70.5</v>
+      </c>
+      <c r="D3" s="45">
+        <v>70.5</v>
+      </c>
+      <c r="E3" s="46">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="52">
+        <v>71.4</v>
+      </c>
+      <c r="D4" s="52">
+        <v>71.4</v>
+      </c>
+      <c r="E4" s="53">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="56">
+        <v>1.0</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="58">
+        <v>72.0</v>
+      </c>
+      <c r="D5" s="58">
+        <v>72.2</v>
+      </c>
+      <c r="E5" s="59">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="64">
+        <v>72.5</v>
+      </c>
+      <c r="D6" s="64">
+        <v>72.4</v>
+      </c>
+      <c r="E6" s="65">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="76">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="78">
+        <v>75.7</v>
+      </c>
+      <c r="D7" s="78">
+        <v>75.7</v>
+      </c>
+      <c r="E7" s="79">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="83">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="85">
+        <v>78.7</v>
+      </c>
+      <c r="D8" s="85">
+        <v>78.7</v>
+      </c>
+      <c r="E8" s="86">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="B9" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="91">
+        <v>80.1</v>
+      </c>
+      <c r="D9" s="91">
+        <v>80.2</v>
+      </c>
+      <c r="E9" s="92">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="36">
+        <v>2.0</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="38">
+        <v>87.0</v>
+      </c>
+      <c r="D10" s="38">
+        <v>86.9</v>
+      </c>
+      <c r="E10" s="39">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43">
+        <v>2.0</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="45">
+        <v>87.7</v>
+      </c>
+      <c r="D11" s="45">
+        <v>87.8</v>
+      </c>
+      <c r="E11" s="46">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="52">
+        <v>89.8</v>
+      </c>
+      <c r="D12" s="52">
+        <v>89.8</v>
+      </c>
+      <c r="E12" s="53">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="56">
+        <v>2.0</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="58">
+        <v>91.6</v>
+      </c>
+      <c r="D13" s="58">
+        <v>91.5</v>
+      </c>
+      <c r="E13" s="59">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="62">
+        <v>2.0</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="64">
+        <v>92.5</v>
+      </c>
+      <c r="D14" s="64">
+        <v>92.5</v>
+      </c>
+      <c r="E14" s="65">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="68">
+        <v>2.0</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="70">
+        <v>92.7</v>
+      </c>
+      <c r="D15" s="70">
+        <v>92.8</v>
+      </c>
+      <c r="E15" s="71">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="76">
+        <v>2.0</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="78">
+        <v>100.6</v>
+      </c>
+      <c r="D16" s="78">
+        <v>100.6</v>
+      </c>
+      <c r="E16" s="79">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="83">
+        <v>2.0</v>
+      </c>
+      <c r="B17" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="85">
+        <v>109.4</v>
+      </c>
+      <c r="D17" s="85">
+        <v>109.6</v>
+      </c>
+      <c r="E17" s="86">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="100">
+        <v>3.0</v>
+      </c>
+      <c r="B18" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="39">
+        <v>109.8</v>
+      </c>
+      <c r="D18" s="39">
+        <v>109.8</v>
+      </c>
+      <c r="E18" s="39">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="102">
+        <v>3.0</v>
+      </c>
+      <c r="B19" s="103" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="104"/>
+      <c r="D19" s="53">
+        <v>114.8</v>
+      </c>
+      <c r="E19" s="53">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="105">
+        <v>3.0</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="65">
+        <v>122.2</v>
+      </c>
+      <c r="D20" s="65">
+        <v>121.9</v>
+      </c>
+      <c r="E20" s="65">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="36">
+        <v>-1.0</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="38">
+        <v>39.3</v>
+      </c>
+      <c r="D21" s="38">
+        <v>39.4</v>
+      </c>
+      <c r="E21" s="38">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43">
+        <v>-1.0</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="45">
+        <v>39.1</v>
+      </c>
+      <c r="D22" s="45">
+        <v>39.1</v>
+      </c>
+      <c r="E22" s="45">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="50">
+        <v>-1.0</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="52">
+        <v>38.2</v>
+      </c>
+      <c r="D23" s="52">
+        <v>38.2</v>
+      </c>
+      <c r="E23" s="52">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56">
+        <v>-1.0</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="58">
+        <v>37.4</v>
+      </c>
+      <c r="D24" s="58">
+        <v>37.4</v>
+      </c>
+      <c r="E24" s="58">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="62">
+        <v>-1.0</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="64">
+        <v>37.1</v>
+      </c>
+      <c r="D25" s="64">
+        <v>37.1</v>
+      </c>
+      <c r="E25" s="64">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="76">
+        <v>-1.0</v>
+      </c>
+      <c r="B26" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="78">
+        <v>33.9</v>
+      </c>
+      <c r="D26" s="78">
+        <v>33.9</v>
+      </c>
+      <c r="E26" s="78">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="83">
+        <v>-1.0</v>
+      </c>
+      <c r="B27" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="85">
+        <v>31.0</v>
+      </c>
+      <c r="D27" s="85">
+        <v>31.0</v>
+      </c>
+      <c r="E27" s="85">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="89">
+        <v>-1.0</v>
+      </c>
+      <c r="B28" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="91">
+        <v>29.5</v>
+      </c>
+      <c r="D28" s="91">
+        <v>29.6</v>
+      </c>
+      <c r="E28" s="91">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="36">
+        <v>-2.0</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="38">
+        <v>22.8</v>
+      </c>
+      <c r="D29" s="38">
+        <v>22.8</v>
+      </c>
+      <c r="E29" s="38">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43">
+        <v>-2.0</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="45">
+        <v>22.1</v>
+      </c>
+      <c r="D30" s="45">
+        <v>22.0</v>
+      </c>
+      <c r="E30" s="45">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50">
+        <v>-2.0</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="52">
+        <v>20.2</v>
+      </c>
+      <c r="D31" s="52">
+        <v>20.0</v>
+      </c>
+      <c r="E31" s="52">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56">
+        <v>-2.0</v>
+      </c>
+      <c r="B32" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="58">
+        <v>18.4</v>
+      </c>
+      <c r="D32" s="58">
+        <v>18.4</v>
+      </c>
+      <c r="E32" s="58">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="62">
+        <v>-2.0</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="64">
+        <v>17.6</v>
+      </c>
+      <c r="D33" s="64">
+        <v>17.5</v>
+      </c>
+      <c r="E33" s="64">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="68">
+        <v>-2.0</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="70">
+        <v>17.3</v>
+      </c>
+      <c r="D34" s="70">
+        <v>17.3</v>
+      </c>
+      <c r="E34" s="70">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="76">
+        <v>-2.0</v>
+      </c>
+      <c r="B35" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="78">
+        <v>9.8</v>
+      </c>
+      <c r="D35" s="78">
+        <v>9.7</v>
+      </c>
+      <c r="E35" s="78">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="83">
+        <v>-2.0</v>
+      </c>
+      <c r="B36" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="85">
+        <v>1.4</v>
+      </c>
+      <c r="D36" s="85">
+        <v>1.4</v>
+      </c>
+      <c r="E36" s="85">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36">
+        <v>-3.0</v>
+      </c>
+      <c r="B37" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="38">
+        <v>2.5</v>
+      </c>
+      <c r="E37" s="38">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43">
+        <v>-3.0</v>
+      </c>
+      <c r="B38" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="44">
+        <v>1.0</v>
+      </c>
+      <c r="D38" s="45">
+        <v>1.1</v>
+      </c>
+      <c r="E38" s="45">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="50">
+        <v>-3.0</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52">
+        <v>356.7</v>
+      </c>
+      <c r="E39" s="52">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56">
+        <v>-3.0</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="58">
+        <v>352.4</v>
+      </c>
+      <c r="D40" s="58">
+        <v>352.5</v>
+      </c>
+      <c r="E40" s="58">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="62">
+        <v>-3.0</v>
+      </c>
+      <c r="B41" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="64">
+        <v>350.3</v>
+      </c>
+      <c r="D41" s="64">
+        <v>350.4</v>
+      </c>
+      <c r="E41" s="64">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="68">
+        <v>-3.0</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="70">
+        <v>349.6</v>
+      </c>
+      <c r="D42" s="70">
+        <v>349.7</v>
+      </c>
+      <c r="E42" s="70">
+        <v>54.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>